--- a/data-raw/arid_sites.xlsx
+++ b/data-raw/arid_sites.xlsx
@@ -1477,7 +1477,7 @@
     <t>20 km south of Iquique</t>
   </si>
   <si>
-    <t>UpperTarapaca Valley</t>
+    <t>Mocha</t>
   </si>
   <si>
     <t>Middle Lluta Valley, Poconchile</t>
@@ -7241,13 +7241,13 @@
         <v>225</v>
       </c>
       <c r="B216">
-        <v>-19.832041</v>
+        <v>-19.81231</v>
       </c>
       <c r="C216">
-        <v>-69.296723</v>
+        <v>-69.28215</v>
       </c>
       <c r="D216">
-        <v>2274</v>
+        <v>1650</v>
       </c>
       <c r="E216" t="s">
         <v>487</v>
@@ -7256,7 +7256,7 @@
         <v>455</v>
       </c>
       <c r="G216" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H216" t="s">
         <v>519</v>
@@ -7265,7 +7265,7 @@
         <v>519</v>
       </c>
       <c r="J216">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="K216">
         <v>1450</v>

--- a/data-raw/arid_sites.xlsx
+++ b/data-raw/arid_sites.xlsx
@@ -7247,7 +7247,7 @@
         <v>-69.28215</v>
       </c>
       <c r="D216">
-        <v>1650</v>
+        <v>2170</v>
       </c>
       <c r="E216" t="s">
         <v>487</v>
@@ -7256,7 +7256,7 @@
         <v>455</v>
       </c>
       <c r="G216" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H216" t="s">
         <v>519</v>

--- a/data-raw/arid_sites.xlsx
+++ b/data-raw/arid_sites.xlsx
@@ -3369,7 +3369,7 @@
         <v>445</v>
       </c>
       <c r="F50" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G50" t="s">
         <v>511</v>
@@ -3398,7 +3398,7 @@
         <v>446</v>
       </c>
       <c r="F51" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G51" t="s">
         <v>511</v>
@@ -3415,7 +3415,7 @@
         <v>446</v>
       </c>
       <c r="F52" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G52" t="s">
         <v>511</v>
@@ -3432,7 +3432,7 @@
         <v>446</v>
       </c>
       <c r="F53" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G53" t="s">
         <v>511</v>
@@ -3449,7 +3449,7 @@
         <v>446</v>
       </c>
       <c r="F54" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G54" t="s">
         <v>511</v>
@@ -3466,7 +3466,7 @@
         <v>446</v>
       </c>
       <c r="F55" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G55" t="s">
         <v>511</v>
@@ -3483,7 +3483,7 @@
         <v>446</v>
       </c>
       <c r="F56" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G56" t="s">
         <v>511</v>
@@ -3500,7 +3500,7 @@
         <v>446</v>
       </c>
       <c r="F57" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G57" t="s">
         <v>511</v>
@@ -3517,7 +3517,7 @@
         <v>446</v>
       </c>
       <c r="F58" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G58" t="s">
         <v>511</v>
@@ -3534,7 +3534,7 @@
         <v>446</v>
       </c>
       <c r="F59" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G59" t="s">
         <v>511</v>
@@ -3551,7 +3551,7 @@
         <v>446</v>
       </c>
       <c r="F60" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G60" t="s">
         <v>511</v>
@@ -3568,7 +3568,7 @@
         <v>446</v>
       </c>
       <c r="F61" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G61" t="s">
         <v>511</v>
@@ -3585,7 +3585,7 @@
         <v>446</v>
       </c>
       <c r="F62" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="G62" t="s">
         <v>511</v>
